--- a/Assets/@Resources/Data/Excel/ItemData.xlsx
+++ b/Assets/@Resources/Data/Excel/ItemData.xlsx
@@ -1,61 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7C3329-E084-4433-A631-69673065D4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+  <si>
+    <t>DataId</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>SpriteName</t>
+  </si>
+  <si>
+    <t>FoundLocation</t>
+  </si>
+  <si>
+    <t>젤리 퐁</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>풍 슬라임이 떨어뜨리는 젤리.</t>
+  </si>
+  <si>
+    <t>신들바람 숲</t>
+  </si>
+  <si>
+    <t>폴짝 젤리</t>
+  </si>
+  <si>
+    <t>라비 슬라임이 떨어뜨리는 젤리.</t>
+  </si>
+  <si>
+    <t>item_rabijelly</t>
+  </si>
+  <si>
+    <t>임시통행증</t>
+  </si>
+  <si>
+    <t>모험가협회에서 발급한 임시 통행증. 숲 입구까지 이동할 수 있다.</t>
+  </si>
+  <si>
+    <t>모험가협회</t>
+  </si>
+  <si>
+    <t>일반통행증</t>
+  </si>
+  <si>
+    <t>1급 모험가에게 발급되는 통행증. 더 넓은 지역으로 이동할 수 있다.</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Slime_Green_Drop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Malgun Gothic"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
+        <fgColor rgb="FF2C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F8E9"/>
+        <fgColor rgb="FFF1F8E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,106 +159,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -456,180 +494,125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DataId</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SpriteName</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FoundLocation</t>
-        </is>
+    <row r="1" spans="1:6" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:6" ht="20" customHeight="1">
+      <c r="A2" s="2">
         <v>1001</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>젤리 퐁</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>풍 슬라임이 떨어뜨리는 젤리.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>item_jellypong</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>신들바람 숲</t>
-        </is>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:6" ht="20" customHeight="1">
+      <c r="A3" s="2">
         <v>1002</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>폴짝 젤리</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>라비 슬라임이 떨어뜨리는 젤리.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>item_rabijelly</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>신들바람 숲</t>
-        </is>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="3">
         <v>9001</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>임시통행증</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>모험가협회에서 발급한 임시 통행증. 숲 입구까지 이동할 수 있다.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>item_temp_pass</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>모험가협회</t>
-        </is>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:6" ht="20" customHeight="1">
+      <c r="A5" s="3">
         <v>9002</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>일반통행증</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>1급 모험가에게 발급되는 통행증. 더 넓은 지역으로 이동할 수 있다.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>item_pass_normal</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>모험가협회</t>
-        </is>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Common,Uncommon,Rare,Epic"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/@Resources/Data/Excel/ItemData.xlsx
+++ b/Assets/@Resources/Data/Excel/ItemData.xlsx
@@ -1,155 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7C3329-E084-4433-A631-69673065D4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InventoryItem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RequisiteItem" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
-  <si>
-    <t>DataId</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>SpriteName</t>
-  </si>
-  <si>
-    <t>FoundLocation</t>
-  </si>
-  <si>
-    <t>젤리 퐁</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>풍 슬라임이 떨어뜨리는 젤리.</t>
-  </si>
-  <si>
-    <t>신들바람 숲</t>
-  </si>
-  <si>
-    <t>폴짝 젤리</t>
-  </si>
-  <si>
-    <t>라비 슬라임이 떨어뜨리는 젤리.</t>
-  </si>
-  <si>
-    <t>item_rabijelly</t>
-  </si>
-  <si>
-    <t>임시통행증</t>
-  </si>
-  <si>
-    <t>모험가협회에서 발급한 임시 통행증. 숲 입구까지 이동할 수 있다.</t>
-  </si>
-  <si>
-    <t>모험가협회</t>
-  </si>
-  <si>
-    <t>일반통행증</t>
-  </si>
-  <si>
-    <t>1급 모험가에게 발급되는 통행증. 더 넓은 지역으로 이동할 수 있다.</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Slime_Green_Drop</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pass1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pass2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Malgun Gothic"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F8E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -157,56 +44,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -494,125 +410,319 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="6" width="20" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="20" customHeight="1">
-      <c r="A3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1">
-      <c r="A4" s="3">
-        <v>9001</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="20" customHeight="1">
-      <c r="A5" s="3">
-        <v>9002</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SpriteName</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FoundLocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ItemJellyPongNameText</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ItemJellyPongDescText</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Slime_Green_Drop</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ItemRabiJellyNameText</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ItemRabiJellyDescText</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>item_rabijelly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ItemPongyaPearlNameText</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ItemPongyaPearlDescText</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SlimeSkill_Drop</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Common,Uncommon,Rare,Epic"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SpriteName</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FoundLocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>20001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ItemTempPermitNameText</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>REQUISITE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ItemTempPermitDescText</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pass1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GuildText</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ItemRegularPermitNameText</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>REQUISITE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ItemRegularPermitDescText</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pass2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GuildText</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>20003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ItemRank2PermitNameText</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>REQUISITE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ItemRank2PermitDescText</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pass4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GuildText</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SpriteName</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FoundLocation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Assets/@Resources/Data/Excel/ItemData.xlsx
+++ b/Assets/@Resources/Data/Excel/ItemData.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,1056 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>10011</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH1NameText</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH1DescText</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Scroll_1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PlaceNameTownAsdalText</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10012</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH2NameText</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH2DescText</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Scroll_2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PlaceNameTownAsdalText</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10013</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH3NameText</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH3DescText</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Scroll_3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PlaceNameTownAsdalText</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10014</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH4NameText</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ItemScrollOfENH4DescText</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Scroll_4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PlaceNameTownAsdalText</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10015</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ItemMORNameText</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ItemMORDescText</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MOR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PlaceNameTownAsdalText</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>11001</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mat11001NameText</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mat11001DescText</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>11002</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mat11002NameText</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mat11002DescText</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11003</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mat11003NameText</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mat11003DescText</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11004</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mat11004NameText</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mat11004DescText</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11005</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mat11005NameText</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mat11005DescText</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_4</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11006</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mat11006NameText</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mat11006DescText</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11007</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mat11007NameText</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mat11007DescText</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_6</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11008</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mat11008NameText</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mat11008DescText</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_7</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11009</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mat11009NameText</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mat11009DescText</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_8</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>11010</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mat11010NameText</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mat11010DescText</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mat_BreezingWindForest_9</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>BreezingWindForestNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>11011</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mat11011NameText</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mat11011DescText</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>11012</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mat11012NameText</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mat11012DescText</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>11013</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mat11013NameText</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mat11013DescText</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>11014</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mat11014NameText</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mat11014DescText</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>11015</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mat11015NameText</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mat11015DescText</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_4</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>11016</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mat11016NameText</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mat11016DescText</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>11017</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mat11017NameText</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mat11017DescText</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_6</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>11018</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mat11018NameText</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mat11018DescText</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_7</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11019</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mat11019NameText</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mat11019DescText</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_8</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>11020</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mat11020NameText</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Mat11020DescText</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mat_WhisperingCave_9</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>WhisperingCaveNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11021</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mat11021NameText</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Mat11021DescText</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>11022</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mat11022NameText</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mat11022DescText</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11023</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mat11023NameText</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Mat11023DescText</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11024</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mat11024NameText</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Mat11024DescText</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11025</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mat11025NameText</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mat11025DescText</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11026</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mat11026NameText</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mat11026DescText</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>11027</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mat11027NameText</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Mat11027DescText</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_6</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11028</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Mat11028NameText</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mat11028DescText</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_7</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11029</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mat11029NameText</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mat11029DescText</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_8</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11030</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mat11030NameText</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mat11030DescText</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mat_RuinedSanctum_9</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>RuinedSanctumNameText</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/ItemData.xlsx
+++ b/Assets/@Resources/Data/Excel/ItemData.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,126 @@
       <c r="F39" t="inlineStr">
         <is>
           <t>RuinedSanctumNameText</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>10016</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ItemSOM1NameText</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ItemSOM1DescText</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SOM1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10017</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ItemSOM2NameText</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ItemSOM2DescText</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SOM2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10018</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ItemSOM3NameText</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ItemSOM3DescText</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SOM3</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>10019</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ItemBMORNameText</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ItemBMORDescText</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BrokenMOR</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PlaceNameBWF0Text</t>
         </is>
       </c>
     </row>
